--- a/excel/butterScaler/butterScaler23-Section05.xlsx
+++ b/excel/butterScaler/butterScaler23-Section05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC96DFC5-2A2C-1347-BA98-E187C3AFFAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805EFFCE-D4CD-3847-8AED-E001FD40C85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="96">
   <si>
     <t>ActionName</t>
   </si>
@@ -297,6 +297,18 @@
   </si>
   <si>
     <t>跪姿腿外展16次</t>
+  </si>
+  <si>
+    <t>从我们的左腿开始</t>
+  </si>
+  <si>
+    <t>腿外展建立姿势</t>
+  </si>
+  <si>
+    <t>腿外展加快建立姿势</t>
+  </si>
+  <si>
+    <t>坚持住</t>
   </si>
 </sst>
 </file>
@@ -667,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -724,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -819,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -988,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1083,7 +1095,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1178,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1273,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1368,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1463,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1532,7 +1544,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
@@ -1638,16 +1650,13 @@
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
-      </c>
-      <c r="E42" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="b">
         <v>0</v>
@@ -1658,16 +1667,16 @@
         <v>82</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -1687,10 +1696,10 @@
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E44" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -1710,10 +1719,10 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -1733,13 +1742,13 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>80</v>
+        <v>64</v>
+      </c>
+      <c r="E46" t="s">
+        <v>70</v>
       </c>
       <c r="F46" t="b">
-        <v>1</v>
-      </c>
-      <c r="G46" t="s">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
@@ -1747,25 +1756,25 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+      <c r="D47" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
         <v>81</v>
       </c>
-      <c r="B47">
-        <v>4</v>
-      </c>
-      <c r="C47">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" t="s">
-        <v>76</v>
-      </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
       <c r="H47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -1779,7 +1788,10 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>85</v>
+        <v>75</v>
+      </c>
+      <c r="E48" t="s">
+        <v>76</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -1799,10 +1811,7 @@
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>77</v>
-      </c>
-      <c r="E49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -1821,14 +1830,14 @@
       <c r="C50">
         <v>4</v>
       </c>
+      <c r="D50" t="s">
+        <v>77</v>
+      </c>
       <c r="E50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F50" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" t="s">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
@@ -1836,22 +1845,25 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
         <v>65</v>
       </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-      <c r="C51">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
-        <v>86</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
       <c r="H51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -1865,12 +1877,1222 @@
         <v>4</v>
       </c>
       <c r="D52" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
         <v>87</v>
       </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52" t="b">
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54">
+        <v>4</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
+        <v>49</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>8</v>
+      </c>
+      <c r="B56">
+        <v>4</v>
+      </c>
+      <c r="C56">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
+        <v>92</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58">
+        <v>8</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" t="s">
+        <v>30</v>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60">
+        <v>8</v>
+      </c>
+      <c r="C60">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61">
+        <v>8</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62">
+        <v>8</v>
+      </c>
+      <c r="C62">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63">
+        <v>8</v>
+      </c>
+      <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64">
+        <v>4</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="F64" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66">
+        <v>4</v>
+      </c>
+      <c r="C66">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" t="s">
+        <v>22</v>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67">
+        <v>4</v>
+      </c>
+      <c r="C67">
+        <v>4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" t="s">
+        <v>23</v>
+      </c>
+      <c r="F67" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68">
+        <v>4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" t="s">
+        <v>26</v>
+      </c>
+      <c r="F68" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B69">
+        <v>4</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" t="s">
+        <v>44</v>
+      </c>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>91</v>
+      </c>
+      <c r="B70">
+        <v>4</v>
+      </c>
+      <c r="C70">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
+        <v>45</v>
+      </c>
+      <c r="E70" t="s">
+        <v>46</v>
+      </c>
+      <c r="F70" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71">
+        <v>4</v>
+      </c>
+      <c r="C71">
+        <v>4</v>
+      </c>
+      <c r="D71" t="s">
+        <v>27</v>
+      </c>
+      <c r="E71" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72">
+        <v>4</v>
+      </c>
+      <c r="C72">
+        <v>4</v>
+      </c>
+      <c r="D72" t="s">
+        <v>47</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73">
+        <v>4</v>
+      </c>
+      <c r="C73">
+        <v>4</v>
+      </c>
+      <c r="D73" t="s">
+        <v>48</v>
+      </c>
+      <c r="E73" t="s">
+        <v>30</v>
+      </c>
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>31</v>
+      </c>
+      <c r="H73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>31</v>
+      </c>
+      <c r="B74">
+        <v>4</v>
+      </c>
+      <c r="C74">
+        <v>4</v>
+      </c>
+      <c r="D74" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>31</v>
+      </c>
+      <c r="B75">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>4</v>
+      </c>
+      <c r="D75" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" t="s">
+        <v>36</v>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76">
+        <v>4</v>
+      </c>
+      <c r="C76">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" t="s">
+        <v>38</v>
+      </c>
+      <c r="F76" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77">
+        <v>4</v>
+      </c>
+      <c r="C77">
+        <v>4</v>
+      </c>
+      <c r="D77" t="s">
+        <v>32</v>
+      </c>
+      <c r="E77" t="s">
+        <v>39</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>32</v>
+      </c>
+      <c r="B78">
+        <v>4</v>
+      </c>
+      <c r="C78">
+        <v>4</v>
+      </c>
+      <c r="D78" t="s">
+        <v>74</v>
+      </c>
+      <c r="E78" t="s">
+        <v>30</v>
+      </c>
+      <c r="F78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>32</v>
+      </c>
+      <c r="B79">
+        <v>4</v>
+      </c>
+      <c r="C79">
+        <v>4</v>
+      </c>
+      <c r="D79" t="s">
+        <v>88</v>
+      </c>
+      <c r="E79" t="s">
+        <v>89</v>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>32</v>
+      </c>
+      <c r="B80">
+        <v>4</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+      <c r="D80" t="s">
+        <v>40</v>
+      </c>
+      <c r="E80" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+      <c r="B81">
+        <v>4</v>
+      </c>
+      <c r="C81">
+        <v>4</v>
+      </c>
+      <c r="D81" t="s">
+        <v>42</v>
+      </c>
+      <c r="E81" t="s">
+        <v>43</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>83</v>
+      </c>
+      <c r="H81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82">
+        <v>4</v>
+      </c>
+      <c r="C82">
+        <v>4</v>
+      </c>
+      <c r="D82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+      <c r="B83">
+        <v>4</v>
+      </c>
+      <c r="C83">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>4</v>
+      </c>
+      <c r="C84">
+        <v>4</v>
+      </c>
+      <c r="D84" t="s">
+        <v>50</v>
+      </c>
+      <c r="E84" t="s">
+        <v>51</v>
+      </c>
+      <c r="F84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85">
+        <v>4</v>
+      </c>
+      <c r="D85" t="s">
+        <v>54</v>
+      </c>
+      <c r="E85" t="s">
+        <v>55</v>
+      </c>
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
+        <v>84</v>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>4</v>
+      </c>
+      <c r="C86">
+        <v>4</v>
+      </c>
+      <c r="D86" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>84</v>
+      </c>
+      <c r="B87">
+        <v>4</v>
+      </c>
+      <c r="C87">
+        <v>4</v>
+      </c>
+      <c r="D87" t="s">
+        <v>52</v>
+      </c>
+      <c r="E87" t="s">
+        <v>53</v>
+      </c>
+      <c r="F87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>84</v>
+      </c>
+      <c r="B88">
+        <v>4</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>56</v>
+      </c>
+      <c r="E88" t="s">
+        <v>57</v>
+      </c>
+      <c r="F88" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>84</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89" t="s">
+        <v>58</v>
+      </c>
+      <c r="E89" t="s">
+        <v>30</v>
+      </c>
+      <c r="F89" t="b">
+        <v>1</v>
+      </c>
+      <c r="G89" t="s">
+        <v>93</v>
+      </c>
+      <c r="H89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>59</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>2</v>
+      </c>
+      <c r="D90" t="s">
+        <v>60</v>
+      </c>
+      <c r="E90" t="s">
+        <v>59</v>
+      </c>
+      <c r="F90" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>59</v>
+      </c>
+      <c r="B91">
+        <v>4</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91" t="s">
+        <v>61</v>
+      </c>
+      <c r="E91" t="s">
+        <v>66</v>
+      </c>
+      <c r="F91" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>59</v>
+      </c>
+      <c r="B92">
+        <v>4</v>
+      </c>
+      <c r="C92">
+        <v>4</v>
+      </c>
+      <c r="D92" t="s">
+        <v>67</v>
+      </c>
+      <c r="E92" t="s">
+        <v>68</v>
+      </c>
+      <c r="F92" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>59</v>
+      </c>
+      <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93">
+        <v>4</v>
+      </c>
+      <c r="D93" t="s">
+        <v>71</v>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>59</v>
+      </c>
+      <c r="B94">
+        <v>4</v>
+      </c>
+      <c r="C94">
+        <v>4</v>
+      </c>
+      <c r="D94" t="s">
+        <v>95</v>
+      </c>
+      <c r="F94" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>82</v>
+      </c>
+      <c r="H94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>59</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95" t="s">
+        <v>72</v>
+      </c>
+      <c r="E95" t="s">
+        <v>73</v>
+      </c>
+      <c r="F95" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>82</v>
+      </c>
+      <c r="B96">
+        <v>4</v>
+      </c>
+      <c r="C96">
+        <v>4</v>
+      </c>
+      <c r="D96" t="s">
+        <v>62</v>
+      </c>
+      <c r="E96" t="s">
+        <v>62</v>
+      </c>
+      <c r="F96" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>82</v>
+      </c>
+      <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97">
+        <v>4</v>
+      </c>
+      <c r="D97" t="s">
+        <v>63</v>
+      </c>
+      <c r="E97" t="s">
+        <v>69</v>
+      </c>
+      <c r="F97" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>82</v>
+      </c>
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98">
+        <v>4</v>
+      </c>
+      <c r="D98" t="s">
+        <v>64</v>
+      </c>
+      <c r="E98" t="s">
+        <v>70</v>
+      </c>
+      <c r="F98" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>82</v>
+      </c>
+      <c r="B99">
+        <v>4</v>
+      </c>
+      <c r="C99">
+        <v>4</v>
+      </c>
+      <c r="D99" t="s">
+        <v>80</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" t="s">
+        <v>81</v>
+      </c>
+      <c r="H99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>81</v>
+      </c>
+      <c r="B100">
+        <v>4</v>
+      </c>
+      <c r="C100">
+        <v>4</v>
+      </c>
+      <c r="D100" t="s">
+        <v>75</v>
+      </c>
+      <c r="E100" t="s">
+        <v>76</v>
+      </c>
+      <c r="F100" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>81</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101" t="s">
+        <v>85</v>
+      </c>
+      <c r="F101" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>81</v>
+      </c>
+      <c r="B102">
+        <v>4</v>
+      </c>
+      <c r="C102">
+        <v>4</v>
+      </c>
+      <c r="D102" t="s">
+        <v>77</v>
+      </c>
+      <c r="E102" t="s">
+        <v>78</v>
+      </c>
+      <c r="F102" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>81</v>
+      </c>
+      <c r="B103">
+        <v>4</v>
+      </c>
+      <c r="C103">
+        <v>4</v>
+      </c>
+      <c r="E103" t="s">
+        <v>79</v>
+      </c>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" t="s">
+        <v>65</v>
+      </c>
+      <c r="H103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>65</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104">
+        <v>4</v>
+      </c>
+      <c r="D104" t="s">
+        <v>86</v>
+      </c>
+      <c r="F104" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>65</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105">
+        <v>4</v>
+      </c>
+      <c r="D105" t="s">
+        <v>87</v>
+      </c>
+      <c r="F105" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" t="b">
         <v>0</v>
       </c>
     </row>

--- a/excel/butterScaler/butterScaler23-Section05.xlsx
+++ b/excel/butterScaler/butterScaler23-Section05.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805EFFCE-D4CD-3847-8AED-E001FD40C85F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37163F12-DACC-5348-A256-69A26BB9D1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="100">
   <si>
     <t>ActionName</t>
   </si>
@@ -309,6 +309,18 @@
   </si>
   <si>
     <t>坚持住</t>
+  </si>
+  <si>
+    <t>还有2次，肚子收紧</t>
+  </si>
+  <si>
+    <t>最后一次</t>
+  </si>
+  <si>
+    <t>1，2</t>
+  </si>
+  <si>
+    <t>2，1</t>
   </si>
 </sst>
 </file>
@@ -327,6 +339,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -822,10 +835,10 @@
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -945,7 +958,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -965,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -991,10 +1004,10 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -1012,12 +1025,6 @@
       </c>
       <c r="C15">
         <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>

--- a/excel/butterScaler/butterScaler23-Section05.xlsx
+++ b/excel/butterScaler/butterScaler23-Section05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37163F12-DACC-5348-A256-69A26BB9D1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C1985E-179F-AE47-ACF9-EFE1FEF64190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1006,9 +1006,6 @@
       <c r="D14" t="s">
         <v>23</v>
       </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
@@ -1026,6 +1023,9 @@
       <c r="C15">
         <v>4</v>
       </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">

--- a/excel/butterScaler/butterScaler23-Section05.xlsx
+++ b/excel/butterScaler/butterScaler23-Section05.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10406"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10407"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C1985E-179F-AE47-ACF9-EFE1FEF64190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20890711-C71F-894B-9D4D-6381825514D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,25 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="101">
   <si>
     <t>ActionName</t>
   </si>
@@ -321,6 +334,9 @@
   </si>
   <si>
     <t>2，1</t>
+  </si>
+  <si>
+    <t>StepActionName</t>
   </si>
 </sst>
 </file>
@@ -692,18 +708,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -711,2395 +728,2398 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
         <v>49</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
         <v>98</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>99</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7">
         <v>8</v>
       </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11">
         <v>8</v>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
         <v>8</v>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12" t="s">
         <v>96</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13">
         <v>8</v>
       </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
         <v>97</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>19</v>
       </c>
-      <c r="F13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" t="s">
         <v>23</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" t="s">
         <v>23</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
         <v>24</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>26</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B17">
         <v>4</v>
       </c>
-      <c r="C17">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" t="s">
         <v>25</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>44</v>
       </c>
-      <c r="F17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
         <v>91</v>
       </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>91</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" t="s">
         <v>45</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>46</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>91</v>
       </c>
       <c r="B19">
         <v>4</v>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
         <v>27</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>28</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>91</v>
       </c>
       <c r="B20">
         <v>4</v>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" t="s">
         <v>47</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>29</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>91</v>
       </c>
       <c r="B21">
         <v>4</v>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
         <v>48</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>30</v>
       </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
         <v>31</v>
       </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>31</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
         <v>33</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>34</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
       <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
         <v>35</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>36</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" t="s">
         <v>37</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>38</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>31</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
-      <c r="C25">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" t="s">
         <v>32</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>39</v>
       </c>
-      <c r="F25" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>32</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
         <v>74</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>30</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>32</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
-      <c r="C27">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="D27">
+        <v>4</v>
+      </c>
+      <c r="E27" t="s">
         <v>88</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>89</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>32</v>
       </c>
       <c r="B28">
         <v>4</v>
       </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28" t="s">
         <v>40</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>41</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" t="s">
         <v>42</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>43</v>
       </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
         <v>83</v>
       </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>83</v>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>22</v>
+      <c r="D30">
+        <v>4</v>
       </c>
       <c r="E30" t="s">
         <v>22</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>83</v>
       </c>
       <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>23</v>
+      <c r="D31">
+        <v>4</v>
       </c>
       <c r="E31" t="s">
         <v>23</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>83</v>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
-      <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="E32" t="s">
         <v>50</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>51</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>83</v>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
-      <c r="C33">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="D33">
+        <v>4</v>
+      </c>
+      <c r="E33" t="s">
         <v>54</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>55</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
         <v>84</v>
       </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>84</v>
       </c>
       <c r="B34">
         <v>4</v>
       </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="D34">
+        <v>4</v>
+      </c>
+      <c r="E34" t="s">
         <v>45</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>46</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>84</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
-      <c r="C35">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" t="s">
         <v>52</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>53</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>84</v>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
-      <c r="C36">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" t="s">
         <v>56</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>57</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>84</v>
       </c>
       <c r="B37">
         <v>4</v>
       </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
         <v>58</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>30</v>
       </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" t="s">
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
         <v>93</v>
       </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>59</v>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>2</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>60</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>59</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>59</v>
       </c>
       <c r="B39">
         <v>4</v>
       </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
         <v>61</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>66</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>59</v>
       </c>
       <c r="B40">
         <v>4</v>
       </c>
-      <c r="C40">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" t="s">
         <v>67</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>68</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>59</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
-      <c r="C41">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
         <v>71</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>59</v>
       </c>
       <c r="B42">
         <v>4</v>
       </c>
-      <c r="C42">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" t="s">
         <v>95</v>
       </c>
-      <c r="F42" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
         <v>94</v>
       </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>82</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>2</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>72</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>73</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>82</v>
       </c>
       <c r="B44">
         <v>4</v>
       </c>
-      <c r="C44">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
-        <v>62</v>
+      <c r="D44">
+        <v>4</v>
       </c>
       <c r="E44" t="s">
         <v>62</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F44" t="s">
+        <v>62</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>82</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
-      <c r="C45">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45" t="s">
         <v>63</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>69</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>82</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
-      <c r="C46">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46" t="s">
         <v>64</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>70</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>82</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
-      <c r="C47">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="E47" t="s">
         <v>80</v>
       </c>
-      <c r="F47" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" t="s">
+      <c r="G47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
         <v>81</v>
       </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>81</v>
       </c>
       <c r="B48">
         <v>4</v>
       </c>
-      <c r="C48">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48" t="s">
         <v>75</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>76</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>81</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
-      <c r="C49">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="D49">
+        <v>4</v>
+      </c>
+      <c r="E49" t="s">
         <v>85</v>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>81</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
-      <c r="C50">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="D50">
+        <v>4</v>
+      </c>
+      <c r="E50" t="s">
         <v>77</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>78</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>81</v>
       </c>
       <c r="B51">
         <v>4</v>
       </c>
-      <c r="C51">
-        <v>4</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="D51">
+        <v>4</v>
+      </c>
+      <c r="F51" t="s">
         <v>79</v>
       </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" t="s">
+      <c r="G51" t="b">
+        <v>1</v>
+      </c>
+      <c r="H51" t="s">
         <v>65</v>
       </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>65</v>
       </c>
       <c r="B52">
         <v>2</v>
       </c>
-      <c r="C52">
-        <v>4</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52" t="s">
         <v>86</v>
       </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>65</v>
       </c>
       <c r="B53">
         <v>2</v>
       </c>
-      <c r="C53">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="D53">
+        <v>4</v>
+      </c>
+      <c r="E53" t="s">
         <v>87</v>
       </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>8</v>
       </c>
       <c r="B54">
         <v>4</v>
       </c>
-      <c r="C54">
-        <v>4</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="D54">
+        <v>4</v>
+      </c>
+      <c r="E54" t="s">
         <v>9</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>11</v>
       </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>8</v>
       </c>
       <c r="B55">
         <v>4</v>
       </c>
-      <c r="C55">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="D55">
+        <v>4</v>
+      </c>
+      <c r="E55" t="s">
         <v>49</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>10</v>
       </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>8</v>
       </c>
       <c r="B56">
         <v>4</v>
       </c>
-      <c r="C56">
-        <v>4</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
         <v>92</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>15</v>
       </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>8</v>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
-      <c r="C57">
-        <v>4</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="D57">
+        <v>4</v>
+      </c>
+      <c r="E57" t="s">
         <v>13</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>14</v>
       </c>
-      <c r="F57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
+      <c r="G57" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
         <v>11</v>
       </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>11</v>
       </c>
       <c r="B58">
         <v>8</v>
       </c>
-      <c r="C58">
-        <v>4</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="D58">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
         <v>74</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>30</v>
       </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>11</v>
       </c>
       <c r="B59">
         <v>8</v>
       </c>
-      <c r="C59">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="D59">
+        <v>4</v>
+      </c>
+      <c r="E59" t="s">
         <v>16</v>
       </c>
-      <c r="F59" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>11</v>
       </c>
       <c r="B60">
         <v>8</v>
       </c>
-      <c r="C60">
-        <v>4</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60" t="s">
         <v>17</v>
       </c>
-      <c r="F60" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>11</v>
       </c>
       <c r="B61">
         <v>8</v>
       </c>
-      <c r="C61">
-        <v>4</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61" t="s">
         <v>18</v>
       </c>
-      <c r="F61" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>11</v>
       </c>
       <c r="B62">
         <v>8</v>
       </c>
-      <c r="C62">
-        <v>4</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62" t="s">
         <v>15</v>
       </c>
-      <c r="F62" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G62" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>11</v>
       </c>
       <c r="B63">
         <v>8</v>
       </c>
-      <c r="C63">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="E63" t="s">
         <v>10</v>
       </c>
-      <c r="F63" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G63" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>11</v>
       </c>
       <c r="B64">
         <v>8</v>
       </c>
-      <c r="C64">
-        <v>4</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="D64">
+        <v>4</v>
+      </c>
+      <c r="E64" t="s">
         <v>20</v>
       </c>
-      <c r="F64" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G64" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>11</v>
       </c>
       <c r="B65">
         <v>8</v>
       </c>
-      <c r="C65">
-        <v>4</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="D65">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
         <v>21</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>19</v>
       </c>
-      <c r="F65" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="G65" t="b">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B66">
         <v>4</v>
       </c>
-      <c r="C66">
-        <v>4</v>
-      </c>
-      <c r="D66" t="s">
-        <v>22</v>
+      <c r="D66">
+        <v>4</v>
       </c>
       <c r="E66" t="s">
         <v>22</v>
       </c>
-      <c r="F66" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F66" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B67">
         <v>4</v>
       </c>
-      <c r="C67">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
-        <v>23</v>
+      <c r="D67">
+        <v>4</v>
       </c>
       <c r="E67" t="s">
         <v>23</v>
       </c>
-      <c r="F67" t="b">
-        <v>0</v>
-      </c>
-      <c r="H67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F67" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B68">
         <v>4</v>
       </c>
-      <c r="C68">
-        <v>4</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="D68">
+        <v>4</v>
+      </c>
+      <c r="E68" t="s">
         <v>24</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>26</v>
       </c>
-      <c r="F68" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B69">
         <v>4</v>
       </c>
-      <c r="C69">
-        <v>4</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69" t="s">
         <v>25</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>44</v>
       </c>
-      <c r="F69" t="b">
-        <v>1</v>
-      </c>
-      <c r="G69" t="s">
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
+      <c r="H69" t="s">
         <v>91</v>
       </c>
-      <c r="H69" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>91</v>
       </c>
       <c r="B70">
         <v>4</v>
       </c>
-      <c r="C70">
-        <v>4</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70" t="s">
         <v>45</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>46</v>
       </c>
-      <c r="F70" t="b">
-        <v>0</v>
-      </c>
-      <c r="H70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>91</v>
       </c>
       <c r="B71">
         <v>4</v>
       </c>
-      <c r="C71">
-        <v>4</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="D71">
+        <v>4</v>
+      </c>
+      <c r="E71" t="s">
         <v>27</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>28</v>
       </c>
-      <c r="F71" t="b">
-        <v>0</v>
-      </c>
-      <c r="H71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G71" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>91</v>
       </c>
       <c r="B72">
         <v>4</v>
       </c>
-      <c r="C72">
-        <v>4</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="D72">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
         <v>47</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>29</v>
       </c>
-      <c r="F72" t="b">
-        <v>0</v>
-      </c>
-      <c r="H72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>91</v>
       </c>
       <c r="B73">
         <v>4</v>
       </c>
-      <c r="C73">
-        <v>4</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="D73">
+        <v>4</v>
+      </c>
+      <c r="E73" t="s">
         <v>48</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>30</v>
       </c>
-      <c r="F73" t="b">
-        <v>1</v>
-      </c>
-      <c r="G73" t="s">
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
+      <c r="H73" t="s">
         <v>31</v>
       </c>
-      <c r="H73" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>31</v>
       </c>
       <c r="B74">
         <v>4</v>
       </c>
-      <c r="C74">
-        <v>4</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74" t="s">
         <v>33</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>34</v>
       </c>
-      <c r="F74" t="b">
-        <v>0</v>
-      </c>
-      <c r="H74" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>31</v>
       </c>
       <c r="B75">
         <v>4</v>
       </c>
-      <c r="C75">
-        <v>4</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="D75">
+        <v>4</v>
+      </c>
+      <c r="E75" t="s">
         <v>35</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>36</v>
       </c>
-      <c r="F75" t="b">
-        <v>0</v>
-      </c>
-      <c r="H75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G75" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>31</v>
       </c>
       <c r="B76">
         <v>4</v>
       </c>
-      <c r="C76">
-        <v>4</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76" t="s">
         <v>37</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>38</v>
       </c>
-      <c r="F76" t="b">
-        <v>0</v>
-      </c>
-      <c r="H76" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G76" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>31</v>
       </c>
       <c r="B77">
         <v>4</v>
       </c>
-      <c r="C77">
-        <v>4</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="D77">
+        <v>4</v>
+      </c>
+      <c r="E77" t="s">
         <v>32</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>39</v>
       </c>
-      <c r="F77" t="b">
-        <v>1</v>
-      </c>
-      <c r="G77" t="s">
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
+      <c r="H77" t="s">
         <v>32</v>
       </c>
-      <c r="H77" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>32</v>
       </c>
       <c r="B78">
         <v>4</v>
       </c>
-      <c r="C78">
-        <v>4</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="D78">
+        <v>4</v>
+      </c>
+      <c r="E78" t="s">
         <v>74</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>30</v>
       </c>
-      <c r="F78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>32</v>
       </c>
       <c r="B79">
         <v>4</v>
       </c>
-      <c r="C79">
-        <v>4</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79" t="s">
         <v>88</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>89</v>
       </c>
-      <c r="F79" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>32</v>
       </c>
       <c r="B80">
         <v>4</v>
       </c>
-      <c r="C80">
-        <v>4</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80" t="s">
         <v>40</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>41</v>
       </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G80" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>32</v>
       </c>
       <c r="B81">
         <v>4</v>
       </c>
-      <c r="C81">
-        <v>4</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="D81">
+        <v>4</v>
+      </c>
+      <c r="E81" t="s">
         <v>42</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>43</v>
       </c>
-      <c r="F81" t="b">
-        <v>1</v>
-      </c>
-      <c r="G81" t="s">
+      <c r="G81" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" t="s">
         <v>83</v>
       </c>
-      <c r="H81" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>83</v>
       </c>
       <c r="B82">
         <v>4</v>
       </c>
-      <c r="C82">
-        <v>4</v>
-      </c>
-      <c r="D82" t="s">
-        <v>22</v>
+      <c r="D82">
+        <v>4</v>
       </c>
       <c r="E82" t="s">
         <v>22</v>
       </c>
-      <c r="F82" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F82" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>83</v>
       </c>
       <c r="B83">
         <v>4</v>
       </c>
-      <c r="C83">
-        <v>4</v>
-      </c>
-      <c r="D83" t="s">
-        <v>23</v>
+      <c r="D83">
+        <v>4</v>
       </c>
       <c r="E83" t="s">
         <v>23</v>
       </c>
-      <c r="F83" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F83" t="s">
+        <v>23</v>
+      </c>
+      <c r="G83" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>83</v>
       </c>
       <c r="B84">
         <v>4</v>
       </c>
-      <c r="C84">
-        <v>4</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84" t="s">
         <v>50</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>51</v>
       </c>
-      <c r="F84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>83</v>
       </c>
       <c r="B85">
         <v>4</v>
       </c>
-      <c r="C85">
-        <v>4</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="D85">
+        <v>4</v>
+      </c>
+      <c r="E85" t="s">
         <v>54</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>55</v>
       </c>
-      <c r="F85" t="b">
-        <v>1</v>
-      </c>
-      <c r="G85" t="s">
+      <c r="G85" t="b">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
         <v>84</v>
       </c>
-      <c r="H85" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>84</v>
       </c>
       <c r="B86">
         <v>4</v>
       </c>
-      <c r="C86">
-        <v>4</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86" t="s">
         <v>45</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>46</v>
       </c>
-      <c r="F86" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G86" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>84</v>
       </c>
       <c r="B87">
         <v>4</v>
       </c>
-      <c r="C87">
-        <v>4</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="D87">
+        <v>4</v>
+      </c>
+      <c r="E87" t="s">
         <v>52</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>53</v>
       </c>
-      <c r="F87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>84</v>
       </c>
       <c r="B88">
         <v>4</v>
       </c>
-      <c r="C88">
-        <v>4</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="E88" t="s">
         <v>56</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>57</v>
       </c>
-      <c r="F88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G88" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>84</v>
       </c>
       <c r="B89">
         <v>4</v>
       </c>
-      <c r="C89">
-        <v>4</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="D89">
+        <v>4</v>
+      </c>
+      <c r="E89" t="s">
         <v>58</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>30</v>
       </c>
-      <c r="F89" t="b">
-        <v>1</v>
-      </c>
-      <c r="G89" t="s">
+      <c r="G89" t="b">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
         <v>93</v>
       </c>
-      <c r="H89" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>59</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
-      <c r="C90">
+      <c r="D90">
         <v>2</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>60</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>59</v>
       </c>
-      <c r="F90" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>59</v>
       </c>
       <c r="B91">
         <v>4</v>
       </c>
-      <c r="C91">
-        <v>4</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="D91">
+        <v>4</v>
+      </c>
+      <c r="E91" t="s">
         <v>61</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>66</v>
       </c>
-      <c r="F91" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>59</v>
       </c>
       <c r="B92">
         <v>4</v>
       </c>
-      <c r="C92">
-        <v>4</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="D92">
+        <v>4</v>
+      </c>
+      <c r="E92" t="s">
         <v>67</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>68</v>
       </c>
-      <c r="F92" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>59</v>
       </c>
       <c r="B93">
         <v>4</v>
       </c>
-      <c r="C93">
-        <v>4</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="D93">
+        <v>4</v>
+      </c>
+      <c r="E93" t="s">
         <v>71</v>
       </c>
-      <c r="F93" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>59</v>
       </c>
       <c r="B94">
         <v>4</v>
       </c>
-      <c r="C94">
-        <v>4</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="D94">
+        <v>4</v>
+      </c>
+      <c r="E94" t="s">
         <v>95</v>
       </c>
-      <c r="F94" t="b">
-        <v>1</v>
-      </c>
-      <c r="G94" t="s">
+      <c r="G94" t="b">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
         <v>82</v>
       </c>
-      <c r="H94" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>59</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
-      <c r="C95">
+      <c r="D95">
         <v>2</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>72</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>73</v>
       </c>
-      <c r="F95" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>82</v>
       </c>
       <c r="B96">
         <v>4</v>
       </c>
-      <c r="C96">
-        <v>4</v>
-      </c>
-      <c r="D96" t="s">
-        <v>62</v>
+      <c r="D96">
+        <v>4</v>
       </c>
       <c r="E96" t="s">
         <v>62</v>
       </c>
-      <c r="F96" t="b">
-        <v>0</v>
-      </c>
-      <c r="H96" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F96" t="s">
+        <v>62</v>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>82</v>
       </c>
       <c r="B97">
         <v>4</v>
       </c>
-      <c r="C97">
-        <v>4</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="D97">
+        <v>4</v>
+      </c>
+      <c r="E97" t="s">
         <v>63</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>69</v>
       </c>
-      <c r="F97" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>82</v>
       </c>
       <c r="B98">
         <v>4</v>
       </c>
-      <c r="C98">
-        <v>4</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="D98">
+        <v>4</v>
+      </c>
+      <c r="E98" t="s">
         <v>64</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>70</v>
       </c>
-      <c r="F98" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>82</v>
       </c>
       <c r="B99">
         <v>4</v>
       </c>
-      <c r="C99">
-        <v>4</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="D99">
+        <v>4</v>
+      </c>
+      <c r="E99" t="s">
         <v>80</v>
       </c>
-      <c r="F99" t="b">
-        <v>1</v>
-      </c>
-      <c r="G99" t="s">
+      <c r="G99" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
         <v>81</v>
       </c>
-      <c r="H99" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>81</v>
       </c>
       <c r="B100">
         <v>4</v>
       </c>
-      <c r="C100">
-        <v>4</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="D100">
+        <v>4</v>
+      </c>
+      <c r="E100" t="s">
         <v>75</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>76</v>
       </c>
-      <c r="F100" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G100" t="b">
+        <v>0</v>
+      </c>
+      <c r="I100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>81</v>
       </c>
       <c r="B101">
         <v>4</v>
       </c>
-      <c r="C101">
-        <v>4</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="D101">
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
         <v>85</v>
       </c>
-      <c r="F101" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G101" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>81</v>
       </c>
       <c r="B102">
         <v>4</v>
       </c>
-      <c r="C102">
-        <v>4</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="D102">
+        <v>4</v>
+      </c>
+      <c r="E102" t="s">
         <v>77</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>78</v>
       </c>
-      <c r="F102" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G102" t="b">
+        <v>0</v>
+      </c>
+      <c r="I102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>81</v>
       </c>
       <c r="B103">
         <v>4</v>
       </c>
-      <c r="C103">
-        <v>4</v>
-      </c>
-      <c r="E103" t="s">
+      <c r="D103">
+        <v>4</v>
+      </c>
+      <c r="F103" t="s">
         <v>79</v>
       </c>
-      <c r="F103" t="b">
-        <v>1</v>
-      </c>
-      <c r="G103" t="s">
+      <c r="G103" t="b">
+        <v>1</v>
+      </c>
+      <c r="H103" t="s">
         <v>65</v>
       </c>
-      <c r="H103" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>65</v>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
-      <c r="C104">
-        <v>4</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="D104">
+        <v>4</v>
+      </c>
+      <c r="E104" t="s">
         <v>86</v>
       </c>
-      <c r="F104" t="b">
-        <v>0</v>
-      </c>
-      <c r="H104" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G104" t="b">
+        <v>0</v>
+      </c>
+      <c r="I104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>65</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
-      <c r="C105">
-        <v>4</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="D105">
+        <v>4</v>
+      </c>
+      <c r="E105" t="s">
         <v>87</v>
       </c>
-      <c r="F105" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" t="b">
+      <c r="G105" t="b">
+        <v>0</v>
+      </c>
+      <c r="I105" t="b">
         <v>0</v>
       </c>
     </row>

--- a/excel/butterScaler/butterScaler23-Section05.xlsx
+++ b/excel/butterScaler/butterScaler23-Section05.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shimin/Desktop/Shimin/4-Hobby/Hileft/CreatingMoviesUsingMusicAndScripts/excel/butterScaler/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20890711-C71F-894B-9D4D-6381825514D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09DD501-E7E9-424D-9BA6-F8C079AB4A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3560" yWindow="-21340" windowWidth="30240" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="99">
   <si>
     <t>ActionName</t>
   </si>
@@ -102,12 +102,6 @@
     <t>还有2个，再来一次</t>
   </si>
   <si>
-    <t>1，2，2，1</t>
-  </si>
-  <si>
-    <t>out, in, out, in</t>
-  </si>
-  <si>
     <t>掌跟用力推地面</t>
   </si>
   <si>
@@ -126,9 +120,6 @@
     <t>少一点回弹</t>
   </si>
   <si>
-    <t>4，3，2，1</t>
-  </si>
-  <si>
     <t>建立侧躺</t>
   </si>
   <si>
@@ -177,9 +168,6 @@
     <t>14，13</t>
   </si>
   <si>
-    <t>还有8个</t>
-  </si>
-  <si>
     <t>加油，最后4个</t>
   </si>
   <si>
@@ -258,21 +246,12 @@
     <t>Single</t>
   </si>
   <si>
-    <t>1，2，3，4</t>
-  </si>
-  <si>
     <t>16,15</t>
   </si>
   <si>
     <t>14,13</t>
   </si>
   <si>
-    <t>8,7</t>
-  </si>
-  <si>
-    <t>6,5</t>
-  </si>
-  <si>
     <t>接下来，停在最高点</t>
   </si>
   <si>
@@ -297,9 +276,6 @@
     <t>wow，快结束了哦</t>
   </si>
   <si>
-    <t>我们都是最棒的</t>
-  </si>
-  <si>
     <t>如果很酸</t>
   </si>
   <si>
@@ -330,20 +306,38 @@
     <t>最后一次</t>
   </si>
   <si>
-    <t>1，2</t>
-  </si>
-  <si>
-    <t>2，1</t>
-  </si>
-  <si>
     <t>StepActionName</t>
+  </si>
+  <si>
+    <t>结束</t>
+  </si>
+  <si>
+    <t>保持身体的稳定</t>
+  </si>
+  <si>
+    <t>还有4秒</t>
+  </si>
+  <si>
+    <t>我们回到最初的四足式</t>
+  </si>
+  <si>
+    <t>膝盖从30度到45度</t>
+  </si>
+  <si>
+    <t>上，下，上，下</t>
+  </si>
+  <si>
+    <t>Very Good</t>
+  </si>
+  <si>
+    <t>稳定住哦</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +357,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -400,12 +400,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -711,12 +712,14 @@
   <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -728,7 +731,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -783,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -854,11 +857,11 @@
       <c r="D6">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
-        <v>98</v>
+      <c r="E6">
+        <v>1221</v>
       </c>
       <c r="F6" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -978,7 +981,7 @@
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
@@ -998,7 +1001,7 @@
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -1007,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
@@ -1015,7 +1018,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -1023,8 +1026,11 @@
       <c r="D14">
         <v>4</v>
       </c>
-      <c r="E14" t="s">
-        <v>23</v>
+      <c r="E14">
+        <v>1212</v>
+      </c>
+      <c r="F14" t="s">
+        <v>96</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -1035,7 +1041,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -1043,8 +1049,11 @@
       <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15" t="s">
-        <v>23</v>
+      <c r="E15">
+        <v>1212</v>
+      </c>
+      <c r="F15" t="s">
+        <v>96</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
@@ -1055,7 +1064,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -1064,10 +1073,10 @@
         <v>4</v>
       </c>
       <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
         <v>24</v>
-      </c>
-      <c r="F16" t="s">
-        <v>26</v>
       </c>
       <c r="G16" t="b">
         <v>0</v>
@@ -1078,7 +1087,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B17">
         <v>4</v>
@@ -1087,16 +1096,16 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I17" t="b">
         <v>0</v>
@@ -1104,7 +1113,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -1113,10 +1122,10 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -1127,7 +1136,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B19">
         <v>4</v>
@@ -1136,10 +1145,10 @@
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
@@ -1150,7 +1159,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B20">
         <v>4</v>
@@ -1158,11 +1167,11 @@
       <c r="D20">
         <v>4</v>
       </c>
-      <c r="E20" t="s">
-        <v>47</v>
+      <c r="E20">
+        <v>8765</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G20" t="b">
         <v>0</v>
@@ -1173,7 +1182,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B21">
         <v>4</v>
@@ -1181,17 +1190,17 @@
       <c r="D21">
         <v>4</v>
       </c>
-      <c r="E21" t="s">
-        <v>48</v>
+      <c r="E21">
+        <v>4321</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -1199,19 +1208,19 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" t="s">
         <v>31</v>
-      </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F22" t="s">
-        <v>34</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
@@ -1222,7 +1231,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B23">
         <v>4</v>
@@ -1231,10 +1240,10 @@
         <v>4</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
@@ -1245,7 +1254,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -1254,10 +1263,10 @@
         <v>4</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G24" t="b">
         <v>0</v>
@@ -1268,7 +1277,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -1277,16 +1286,16 @@
         <v>4</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F25" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -1294,7 +1303,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -1302,11 +1311,11 @@
       <c r="D26">
         <v>4</v>
       </c>
-      <c r="E26" t="s">
-        <v>74</v>
+      <c r="E26">
+        <v>1221</v>
       </c>
       <c r="F26" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G26" t="b">
         <v>0</v>
@@ -1317,7 +1326,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>4</v>
@@ -1326,10 +1335,10 @@
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
@@ -1340,7 +1349,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B28">
         <v>4</v>
@@ -1349,10 +1358,10 @@
         <v>4</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G28" t="b">
         <v>0</v>
@@ -1363,7 +1372,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -1372,16 +1381,16 @@
         <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F29" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -1389,7 +1398,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B30">
         <v>4</v>
@@ -1397,11 +1406,11 @@
       <c r="D30">
         <v>4</v>
       </c>
-      <c r="E30" t="s">
-        <v>22</v>
+      <c r="E30">
+        <v>1212</v>
       </c>
       <c r="F30" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="G30" t="b">
         <v>0</v>
@@ -1412,7 +1421,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B31">
         <v>4</v>
@@ -1420,11 +1429,11 @@
       <c r="D31">
         <v>4</v>
       </c>
-      <c r="E31" t="s">
-        <v>23</v>
+      <c r="E31">
+        <v>1212</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
@@ -1435,7 +1444,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B32">
         <v>4</v>
@@ -1444,10 +1453,10 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G32" t="b">
         <v>0</v>
@@ -1458,7 +1467,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B33">
         <v>4</v>
@@ -1467,16 +1476,16 @@
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G33" t="b">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -1484,7 +1493,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B34">
         <v>4</v>
@@ -1493,10 +1502,10 @@
         <v>4</v>
       </c>
       <c r="E34" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
@@ -1507,7 +1516,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B35">
         <v>4</v>
@@ -1516,10 +1525,10 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
@@ -1530,7 +1539,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -1539,10 +1548,10 @@
         <v>4</v>
       </c>
       <c r="E36" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G36" t="b">
         <v>0</v>
@@ -1553,7 +1562,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -1561,17 +1570,17 @@
       <c r="D37">
         <v>4</v>
       </c>
-      <c r="E37" t="s">
-        <v>58</v>
+      <c r="E37">
+        <v>4321</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="G37" t="b">
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -1579,7 +1588,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -1588,10 +1597,10 @@
         <v>2</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G38" t="b">
         <v>0</v>
@@ -1602,7 +1611,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B39">
         <v>4</v>
@@ -1611,10 +1620,10 @@
         <v>4</v>
       </c>
       <c r="E39" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F39" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G39" t="b">
         <v>0</v>
@@ -1625,7 +1634,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -1634,10 +1643,10 @@
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F40" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G40" t="b">
         <v>0</v>
@@ -1648,7 +1657,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B41">
         <v>4</v>
@@ -1657,7 +1666,7 @@
         <v>4</v>
       </c>
       <c r="E41" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G41" t="b">
         <v>0</v>
@@ -1668,7 +1677,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -1677,13 +1686,13 @@
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -1691,7 +1700,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -1700,10 +1709,10 @@
         <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F43" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G43" t="b">
         <v>0</v>
@@ -1714,7 +1723,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B44">
         <v>4</v>
@@ -1722,11 +1731,11 @@
       <c r="D44">
         <v>4</v>
       </c>
-      <c r="E44" t="s">
-        <v>62</v>
+      <c r="E44">
+        <v>1212</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="G44" t="b">
         <v>0</v>
@@ -1737,7 +1746,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -1746,10 +1755,10 @@
         <v>4</v>
       </c>
       <c r="E45" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F45" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G45" t="b">
         <v>0</v>
@@ -1760,7 +1769,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B46">
         <v>4</v>
@@ -1769,10 +1778,10 @@
         <v>4</v>
       </c>
       <c r="E46" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G46" t="b">
         <v>0</v>
@@ -1783,7 +1792,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B47">
         <v>4</v>
@@ -1792,13 +1801,13 @@
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G47" t="b">
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -1806,7 +1815,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B48">
         <v>4</v>
@@ -1815,10 +1824,10 @@
         <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F48" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G48" t="b">
         <v>0</v>
@@ -1829,7 +1838,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B49">
         <v>4</v>
@@ -1838,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G49" t="b">
         <v>0</v>
@@ -1849,7 +1858,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B50">
         <v>4</v>
@@ -1857,11 +1866,8 @@
       <c r="D50">
         <v>4</v>
       </c>
-      <c r="E50" t="s">
-        <v>77</v>
-      </c>
-      <c r="F50" t="s">
-        <v>78</v>
+      <c r="E50">
+        <v>8765</v>
       </c>
       <c r="G50" t="b">
         <v>0</v>
@@ -1872,7 +1878,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B51">
         <v>4</v>
@@ -1880,14 +1886,17 @@
       <c r="D51">
         <v>4</v>
       </c>
+      <c r="E51">
+        <v>4321</v>
+      </c>
       <c r="F51" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G51" t="b">
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -1895,7 +1904,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -1904,7 +1913,7 @@
         <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G52" t="b">
         <v>0</v>
@@ -1915,7 +1924,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -1924,7 +1933,7 @@
         <v>4</v>
       </c>
       <c r="E53" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G53" t="b">
         <v>0</v>
@@ -1944,10 +1953,7 @@
         <v>4</v>
       </c>
       <c r="E54" t="s">
-        <v>9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="G54" t="b">
         <v>0</v>
@@ -1967,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="E55" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F55" t="s">
         <v>10</v>
@@ -1990,7 +1996,7 @@
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F56" t="s">
         <v>15</v>
@@ -2038,11 +2044,11 @@
       <c r="D58">
         <v>4</v>
       </c>
-      <c r="E58" t="s">
-        <v>74</v>
+      <c r="E58">
+        <v>1221</v>
       </c>
       <c r="F58" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G58" t="b">
         <v>0</v>
@@ -2191,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I65" t="b">
         <v>0</v>
@@ -2199,7 +2205,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B66">
         <v>4</v>
@@ -2207,11 +2213,8 @@
       <c r="D66">
         <v>4</v>
       </c>
-      <c r="E66" t="s">
-        <v>22</v>
-      </c>
-      <c r="F66" t="s">
-        <v>22</v>
+      <c r="E66">
+        <v>1212</v>
       </c>
       <c r="G66" t="b">
         <v>0</v>
@@ -2222,7 +2225,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B67">
         <v>4</v>
@@ -2230,11 +2233,8 @@
       <c r="D67">
         <v>4</v>
       </c>
-      <c r="E67" t="s">
-        <v>23</v>
-      </c>
-      <c r="F67" t="s">
-        <v>23</v>
+      <c r="E67">
+        <v>1212</v>
       </c>
       <c r="G67" t="b">
         <v>0</v>
@@ -2245,7 +2245,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B68">
         <v>4</v>
@@ -2254,10 +2254,10 @@
         <v>4</v>
       </c>
       <c r="E68" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" t="s">
         <v>24</v>
-      </c>
-      <c r="F68" t="s">
-        <v>26</v>
       </c>
       <c r="G68" t="b">
         <v>0</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B69">
         <v>4</v>
@@ -2277,16 +2277,16 @@
         <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F69" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G69" t="b">
         <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B70">
         <v>4</v>
@@ -2303,10 +2303,10 @@
         <v>4</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F70" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G70" t="b">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B71">
         <v>4</v>
@@ -2326,10 +2326,7 @@
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="G71" t="b">
         <v>0</v>
@@ -2340,7 +2337,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B72">
         <v>4</v>
@@ -2348,11 +2345,11 @@
       <c r="D72">
         <v>4</v>
       </c>
-      <c r="E72" t="s">
-        <v>47</v>
+      <c r="E72">
+        <v>8765</v>
       </c>
       <c r="F72" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G72" t="b">
         <v>0</v>
@@ -2363,7 +2360,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B73">
         <v>4</v>
@@ -2371,17 +2368,17 @@
       <c r="D73">
         <v>4</v>
       </c>
-      <c r="E73" t="s">
-        <v>48</v>
+      <c r="E73">
+        <v>4321</v>
       </c>
       <c r="F73" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G73" t="b">
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -2389,19 +2386,19 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74">
+        <v>4</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74" t="s">
+        <v>30</v>
+      </c>
+      <c r="F74" t="s">
         <v>31</v>
-      </c>
-      <c r="B74">
-        <v>4</v>
-      </c>
-      <c r="D74">
-        <v>4</v>
-      </c>
-      <c r="E74" t="s">
-        <v>33</v>
-      </c>
-      <c r="F74" t="s">
-        <v>34</v>
       </c>
       <c r="G74" t="b">
         <v>0</v>
@@ -2412,7 +2409,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B75">
         <v>4</v>
@@ -2421,10 +2418,10 @@
         <v>4</v>
       </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F75" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
@@ -2435,7 +2432,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B76">
         <v>4</v>
@@ -2444,10 +2441,10 @@
         <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F76" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G76" t="b">
         <v>0</v>
@@ -2458,7 +2455,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B77">
         <v>4</v>
@@ -2467,16 +2464,16 @@
         <v>4</v>
       </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F77" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G77" t="b">
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
@@ -2484,7 +2481,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B78">
         <v>4</v>
@@ -2492,11 +2489,8 @@
       <c r="D78">
         <v>4</v>
       </c>
-      <c r="E78" t="s">
-        <v>74</v>
-      </c>
-      <c r="F78" t="s">
-        <v>30</v>
+      <c r="E78">
+        <v>1221</v>
       </c>
       <c r="G78" t="b">
         <v>0</v>
@@ -2507,7 +2501,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B79">
         <v>4</v>
@@ -2516,10 +2510,10 @@
         <v>4</v>
       </c>
       <c r="E79" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F79" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G79" t="b">
         <v>0</v>
@@ -2530,7 +2524,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B80">
         <v>4</v>
@@ -2539,10 +2533,10 @@
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F80" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G80" t="b">
         <v>0</v>
@@ -2553,7 +2547,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B81">
         <v>4</v>
@@ -2562,16 +2556,16 @@
         <v>4</v>
       </c>
       <c r="E81" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G81" t="b">
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I81" t="b">
         <v>0</v>
@@ -2579,7 +2573,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B82">
         <v>4</v>
@@ -2587,11 +2581,11 @@
       <c r="D82">
         <v>4</v>
       </c>
-      <c r="E82" t="s">
-        <v>22</v>
-      </c>
-      <c r="F82" t="s">
-        <v>22</v>
+      <c r="E82">
+        <v>1212</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="G82" t="b">
         <v>0</v>
@@ -2602,7 +2596,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B83">
         <v>4</v>
@@ -2610,11 +2604,11 @@
       <c r="D83">
         <v>4</v>
       </c>
-      <c r="E83" t="s">
-        <v>23</v>
-      </c>
-      <c r="F83" t="s">
-        <v>23</v>
+      <c r="E83">
+        <v>1212</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="G83" t="b">
         <v>0</v>
@@ -2625,7 +2619,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B84">
         <v>4</v>
@@ -2634,10 +2628,10 @@
         <v>4</v>
       </c>
       <c r="E84" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F84" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G84" t="b">
         <v>0</v>
@@ -2648,7 +2642,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B85">
         <v>4</v>
@@ -2657,16 +2651,16 @@
         <v>4</v>
       </c>
       <c r="E85" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F85" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I85" t="b">
         <v>0</v>
@@ -2674,7 +2668,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B86">
         <v>4</v>
@@ -2683,10 +2677,10 @@
         <v>4</v>
       </c>
       <c r="E86" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F86" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G86" t="b">
         <v>0</v>
@@ -2697,7 +2691,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B87">
         <v>4</v>
@@ -2706,10 +2700,10 @@
         <v>4</v>
       </c>
       <c r="E87" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F87" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G87" t="b">
         <v>0</v>
@@ -2720,7 +2714,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B88">
         <v>4</v>
@@ -2728,11 +2722,11 @@
       <c r="D88">
         <v>4</v>
       </c>
-      <c r="E88" t="s">
-        <v>56</v>
+      <c r="E88">
+        <v>8765</v>
       </c>
       <c r="F88" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G88" t="b">
         <v>0</v>
@@ -2743,7 +2737,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B89">
         <v>4</v>
@@ -2751,17 +2745,17 @@
       <c r="D89">
         <v>4</v>
       </c>
-      <c r="E89" t="s">
-        <v>58</v>
+      <c r="E89">
+        <v>4321</v>
       </c>
       <c r="F89" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G89" t="b">
         <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
@@ -2769,7 +2763,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -2778,10 +2772,10 @@
         <v>2</v>
       </c>
       <c r="E90" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F90" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
@@ -2792,7 +2786,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B91">
         <v>4</v>
@@ -2801,10 +2795,10 @@
         <v>4</v>
       </c>
       <c r="E91" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F91" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G91" t="b">
         <v>0</v>
@@ -2815,7 +2809,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B92">
         <v>4</v>
@@ -2824,10 +2818,10 @@
         <v>4</v>
       </c>
       <c r="E92" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F92" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G92" t="b">
         <v>0</v>
@@ -2838,7 +2832,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B93">
         <v>4</v>
@@ -2847,7 +2841,7 @@
         <v>4</v>
       </c>
       <c r="E93" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G93" t="b">
         <v>0</v>
@@ -2858,7 +2852,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B94">
         <v>4</v>
@@ -2867,13 +2861,13 @@
         <v>4</v>
       </c>
       <c r="E94" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G94" t="b">
         <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I94" t="b">
         <v>0</v>
@@ -2881,7 +2875,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -2890,10 +2884,10 @@
         <v>2</v>
       </c>
       <c r="E95" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F95" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G95" t="b">
         <v>0</v>
@@ -2904,7 +2898,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B96">
         <v>4</v>
@@ -2912,11 +2906,11 @@
       <c r="D96">
         <v>4</v>
       </c>
-      <c r="E96" t="s">
-        <v>62</v>
-      </c>
-      <c r="F96" t="s">
-        <v>62</v>
+      <c r="E96">
+        <v>1212</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="G96" t="b">
         <v>0</v>
@@ -2927,7 +2921,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B97">
         <v>4</v>
@@ -2936,10 +2930,10 @@
         <v>4</v>
       </c>
       <c r="E97" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F97" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G97" t="b">
         <v>0</v>
@@ -2950,7 +2944,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B98">
         <v>4</v>
@@ -2959,10 +2953,10 @@
         <v>4</v>
       </c>
       <c r="E98" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F98" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
@@ -2973,7 +2967,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B99">
         <v>4</v>
@@ -2982,13 +2976,13 @@
         <v>4</v>
       </c>
       <c r="E99" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G99" t="b">
         <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I99" t="b">
         <v>0</v>
@@ -2996,7 +2990,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B100">
         <v>4</v>
@@ -3005,10 +2999,10 @@
         <v>4</v>
       </c>
       <c r="E100" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F100" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G100" t="b">
         <v>0</v>
@@ -3019,7 +3013,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B101">
         <v>4</v>
@@ -3028,7 +3022,7 @@
         <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G101" t="b">
         <v>0</v>
@@ -3039,7 +3033,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B102">
         <v>4</v>
@@ -3047,11 +3041,8 @@
       <c r="D102">
         <v>4</v>
       </c>
-      <c r="E102" t="s">
-        <v>77</v>
-      </c>
-      <c r="F102" t="s">
-        <v>78</v>
+      <c r="E102">
+        <v>8765</v>
       </c>
       <c r="G102" t="b">
         <v>0</v>
@@ -3062,7 +3053,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B103">
         <v>4</v>
@@ -3070,14 +3061,17 @@
       <c r="D103">
         <v>4</v>
       </c>
+      <c r="E103">
+        <v>4321</v>
+      </c>
       <c r="F103" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G103" t="b">
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="I103" t="b">
         <v>0</v>
@@ -3085,7 +3079,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B104">
         <v>2</v>
@@ -3094,7 +3088,7 @@
         <v>4</v>
       </c>
       <c r="E104" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G104" t="b">
         <v>0</v>
@@ -3103,9 +3097,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B105">
         <v>2</v>
@@ -3114,10 +3108,13 @@
         <v>4</v>
       </c>
       <c r="E105" t="s">
-        <v>87</v>
-      </c>
-      <c r="G105" t="b">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="G105" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105" t="s">
+        <v>91</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
